--- a/testcase.xlsx
+++ b/testcase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\mfec\BA_TOOL_For_multiple_DB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D4537AC-C62D-41E1-9AB8-26E947DB942E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA432532-F33C-4EF5-AB4A-9847D83943A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="175">
   <si>
     <t>รหัสกรณีทดสอบ</t>
   </si>
@@ -557,6 +557,9 @@
   </si>
   <si>
     <t>ยังไม่ได้ทำ logic รองรับการทำงานที่แพโหลดเพื่อแปลงไฟล์ csv หรือ xlsx แปลงไปยัง sql</t>
+  </si>
+  <si>
+    <t>หมายเหตุ</t>
   </si>
 </sst>
 </file>
@@ -616,7 +619,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -650,25 +653,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -679,16 +669,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -703,9 +687,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1107,6 +1088,9 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1133,6 +1117,7 @@
       <c r="H2" s="3" t="s">
         <v>150</v>
       </c>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1156,9 +1141,10 @@
       <c r="G3" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -1180,10 +1166,10 @@
         <v>152</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I4" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1200,7 +1186,7 @@
       <c r="D5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1209,9 +1195,10 @@
       <c r="G5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H5" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
@@ -1233,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1260,10 +1247,10 @@
         <v>31</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1287,10 +1274,10 @@
         <v>35</v>
       </c>
       <c r="G8" s="2"/>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1314,10 +1301,10 @@
         <v>39</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1341,10 +1328,10 @@
         <v>43</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1368,10 +1355,10 @@
         <v>47</v>
       </c>
       <c r="G11" s="2"/>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1395,10 +1382,10 @@
         <v>51</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1422,10 +1409,10 @@
         <v>55</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1449,10 +1436,10 @@
         <v>59</v>
       </c>
       <c r="G14" s="2"/>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="2" t="s">
         <v>173</v>
       </c>
     </row>
@@ -1475,12 +1462,13 @@
       <c r="F15" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H15" s="9" t="s">
-        <v>150</v>
-      </c>
+      <c r="H15" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I15" s="8"/>
     </row>
     <row r="16" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
@@ -1504,10 +1492,10 @@
       <c r="G16" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="H16" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="I16" s="7"/>
+      <c r="H16" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -1531,9 +1519,10 @@
       <c r="G17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H17" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I17" s="8"/>
     </row>
     <row r="18" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
@@ -1557,9 +1546,10 @@
       <c r="G18" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H18" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" s="8"/>
     </row>
     <row r="19" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
@@ -1583,9 +1573,10 @@
       <c r="G19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H19" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I19" s="8"/>
     </row>
     <row r="20" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
@@ -1609,9 +1600,10 @@
       <c r="G20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="8"/>
     </row>
     <row r="21" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
@@ -1635,9 +1627,10 @@
       <c r="G21" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H21" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H21" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I21" s="8"/>
     </row>
     <row r="22" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
@@ -1661,9 +1654,10 @@
       <c r="G22" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H22" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I22" s="8"/>
     </row>
     <row r="23" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
@@ -1687,9 +1681,10 @@
       <c r="G23" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H23" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
@@ -1713,9 +1708,10 @@
       <c r="G24" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H24" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I24" s="8"/>
     </row>
     <row r="25" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
@@ -1739,9 +1735,10 @@
       <c r="G25" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="H25" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H25" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" s="8"/>
     </row>
     <row r="26" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
@@ -1765,10 +1762,10 @@
       <c r="G26" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="I26" s="4"/>
+      <c r="H26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I26" s="6"/>
     </row>
     <row r="27" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
@@ -1792,9 +1789,10 @@
       <c r="G27" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="6" t="s">
         <v>164</v>
       </c>
+      <c r="I27" s="8"/>
     </row>
     <row r="28" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
@@ -1818,9 +1816,10 @@
       <c r="G28" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H28" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
@@ -1844,9 +1843,10 @@
       <c r="G29" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H29" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I29" s="8"/>
     </row>
     <row r="30" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
@@ -1870,9 +1870,10 @@
       <c r="G30" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>150</v>
-      </c>
+      <c r="H30" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I30" s="8"/>
     </row>
     <row r="31" spans="1:9" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
@@ -1896,9 +1897,10 @@
       <c r="G31" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="6" t="s">
         <v>164</v>
       </c>
+      <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
@@ -1922,11 +1924,12 @@
       <c r="G32" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H32" s="6" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>124</v>
       </c>
@@ -1948,11 +1951,12 @@
       <c r="G33" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="H33" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H33" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>127</v>
       </c>
@@ -1974,11 +1978,12 @@
       <c r="G34" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="H34" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H34" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>131</v>
       </c>
@@ -2000,11 +2005,12 @@
       <c r="G35" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="H35" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H35" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>135</v>
       </c>
@@ -2026,11 +2032,12 @@
       <c r="G36" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="6" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>139</v>
       </c>
@@ -2052,11 +2059,12 @@
       <c r="G37" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H37" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H37" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>143</v>
       </c>
@@ -2078,11 +2086,12 @@
       <c r="G38" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H38" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="1:9" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>147</v>
       </c>
@@ -2104,48 +2113,49 @@
       <c r="G39" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="H39" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="12" t="s">
+      <c r="H39" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C41" s="12"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C41" s="10"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C42" s="10">
+      <c r="C42" s="8">
         <f>COUNTIF(H2:H100, "Pass")</f>
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="10">
+      <c r="C43" s="8">
         <f>COUNTIF(H2:H100, "Fail")</f>
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C44" s="10">
+      <c r="C44" s="8">
         <f>COUNTIF(H2:H100, "N/A")</f>
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="8">
         <f>COUNTIF(H2:H100, "Pending")</f>
         <v>0</v>
       </c>
